--- a/apps/easi/www/calculator/EASI_Calculator_1.0.xlsx
+++ b/apps/easi/www/calculator/EASI_Calculator_1.0.xlsx
@@ -5811,7 +5811,7 @@
         </is>
       </c>
       <c r="B90" s="123">
-        <f>IF(COUNT('EASI Score'!$B$89:$M$89)&lt;12,"",IF(AVERAGE('EASI Score'!$B$89:$M$89)&lt;=0,"",ROUND(STDEV.P('EASI Score'!$B$89:$M$89)/AVERAGE('EASI Score'!$B$89:$M$89),6)))</f>
+        <f>IF(COUNT('EASI Score'!$B$89:$M$89)&lt;12,"",IF(AVERAGE('EASI Score'!$B$89:$M$89)&lt;=0,"",ROUND(_xlfn.STDEV.P('EASI Score'!$B$89:$M$89)/AVERAGE('EASI Score'!$B$89:$M$89),6)))</f>
         <v/>
       </c>
       <c r="C90" s="124" t="inlineStr">
@@ -6299,20 +6299,20 @@
     <dataValidation sqref="J30" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Entry refused" error="Pick Good, Fair or Poor, or leave the cell blank." promptTitle="Override Score (Optional)" prompt="Optional. Pick Good, Fair or Poor to override this function's computed rating and score, as a rating changed on the EASI Assessment page does. Leave blank to keep the computed rating." type="list" errorStyle="stop">
       <formula1>"Good,Fair,Poor"</formula1>
     </dataValidation>
-    <dataValidation sqref="J33" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Entry refused" error="Pick Good, Fair or Poor, or leave the cell blank." promptTitle="Observed channel-evolution class" prompt="Good, Fair or Poor from a documented field assessment. Applies only with the note below." type="list" errorStyle="stop">
+    <dataValidation sqref="J33" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Entry refused" error="Pick Good, Fair or Poor, or leave the cell blank." promptTitle="Observed channel-evolution class" prompt="Good: Stable or recovered Stage I/VI condition. Fair: Moderate adjustment or recovery, generally Stages III-V. Poor: Severe incision or destructive adjustment, generally Stage II or severe III-IV. From a field visit or report. Needs the note below." type="list" errorStyle="stop">
       <formula1>"Good,Fair,Poor"</formula1>
     </dataValidation>
-    <dataValidation sqref="J34" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Observed channel-evolution indic" prompt="Required for the observed class to replace the automatic proxy." type="custom">
+    <dataValidation sqref="J34" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Observed channel-evolution indic" prompt="Required for the observed class to apply. Record what was seen (headcuts, bars, width or depth change, bank erosion, recovery features) with the source and the date." type="custom">
       <formula1>TRUE</formula1>
     </dataValidation>
     <dataValidation sqref="J35" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Entry refused" error="Pick Good, Fair or Poor, or leave the cell blank." promptTitle="Override Score (Optional)" prompt="Optional. Pick Good, Fair or Poor to override this function's computed rating and score, as a rating changed on the EASI Assessment page does. Complete observed entries above take precedence. Leave blank to keep the computed rating." type="list" errorStyle="stop">
       <formula1>"Good,Fair,Poor"</formula1>
     </dataValidation>
-    <dataValidation sqref="J37" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Entry refused" error="Enter a percentage from 0 to 100, or leave the cell blank." promptTitle="Observed eroding bank" prompt="Percent of bank length eroding, from field or verified imagery. Both bank entries are required." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="J37" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Entry refused" error="Enter a percentage from 0 to 100, or leave the cell blank." promptTitle="Observed eroding bank" prompt="Percent of bank length eroding, from a field visit or verified imagery. Good &lt;5%, Fair 5-&lt;60%, Poor ≥60%. Both bank entries are required and the worse governs." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation sqref="J38" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Entry refused" error="Enter a percentage from 0 to 100, or leave the cell blank." promptTitle="Observed armored bank" prompt="Percent of bank length armored." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="J38" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Entry refused" error="Enter a percentage from 0 to 100, or leave the cell blank." promptTitle="Observed armored bank" prompt="Percent of bank length artificially armored. Good 0%, Fair &gt;0-&lt;50%, Poor ≥50%. Both bank entries are required and the worse governs." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>79d483d27fb2ef67486d4807aa617d736f40eb89936a68d4075c302601c2f82f</t>
+          <t>03e547f88190586d9dc3bff23c93d2b8cd73302b7108d6df37ff3e8432855f19</t>
         </is>
       </c>
     </row>
